--- a/06-business-plan-pitch-deck/Business_Plan_Model.xlsx
+++ b/06-business-plan-pitch-deck/Business_Plan_Model.xlsx
@@ -36,6 +36,28 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Base de calcul : le produit financier (P&amp;L, ligne "Produits financiers") est calculé sur la trésorerie d'ouverture de l'exercice (avant les flux de l'année), par simplification. C'est une base légèrement conservatrice par rapport à un calcul sur la trésorerie moyenne de la période, qui donnerait un produit financier un peu plus élevé les années de forte génération de cash.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="167">
   <si>
@@ -554,7 +576,7 @@
     <numFmt numFmtId="170" formatCode="#,##0"/>
     <numFmt numFmtId="171" formatCode="#,##0.0;\(#,##0.0\);\-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,6 +649,11 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -732,103 +759,103 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1035,11 +1062,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61919637"/>
-        <c:axId val="77235343"/>
+        <c:axId val="62384329"/>
+        <c:axId val="24836139"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61919637"/>
+        <c:axId val="62384329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1071,7 +1098,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77235343"/>
+        <c:crossAx val="24836139"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1079,7 +1106,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77235343"/>
+        <c:axId val="24836139"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1121,7 +1148,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61919637"/>
+        <c:crossAx val="62384329"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1297,8 +1324,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70603405"/>
-        <c:axId val="20984796"/>
+        <c:axId val="52626626"/>
+        <c:axId val="34672141"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1423,11 +1450,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="34348821"/>
-        <c:axId val="70515276"/>
+        <c:axId val="51594492"/>
+        <c:axId val="5627408"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70603405"/>
+        <c:axId val="52626626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1459,7 +1486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20984796"/>
+        <c:crossAx val="34672141"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1467,7 +1494,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20984796"/>
+        <c:axId val="34672141"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1543,12 +1570,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70603405"/>
+        <c:crossAx val="52626626"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="34348821"/>
+        <c:axId val="51594492"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1580,7 +1607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70515276"/>
+        <c:crossAx val="5627408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1588,7 +1615,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70515276"/>
+        <c:axId val="5627408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1654,7 +1681,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34348821"/>
+        <c:crossAx val="51594492"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1830,11 +1857,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="2887948"/>
-        <c:axId val="28430908"/>
+        <c:axId val="79329690"/>
+        <c:axId val="45734870"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2887948"/>
+        <c:axId val="79329690"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1866,7 +1893,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28430908"/>
+        <c:crossAx val="45734870"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1874,7 +1901,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28430908"/>
+        <c:axId val="45734870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1950,7 +1977,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2887948"/>
+        <c:crossAx val="79329690"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1989,9 +2016,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>331920</xdr:colOff>
+      <xdr:colOff>330480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>182520</xdr:rowOff>
+      <xdr:rowOff>181080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2000,7 +2027,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="611640" y="5333040"/>
-        <a:ext cx="5759280" cy="2878920"/>
+        <a:ext cx="5757840" cy="2877480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2024,9 +2051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>339480</xdr:colOff>
+      <xdr:colOff>338040</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2035,7 +2062,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="611640" y="4190040"/>
-        <a:ext cx="6119280" cy="3239280"/>
+        <a:ext cx="6117840" cy="3237840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2054,9 +2081,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>4320</xdr:colOff>
+      <xdr:colOff>2880</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2065,7 +2092,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9587880" y="4190040"/>
-        <a:ext cx="6119280" cy="3239280"/>
+        <a:ext cx="6117840" cy="3237840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2938,6 +2965,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
